--- a/public/files/danh_sach_nha_cung_cap_mau.xlsx
+++ b/public/files/danh_sach_nha_cung_cap_mau.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\job-part-time\nextjs-antd-admin\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E57358-EBBD-4902-AB70-6A304F603F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0940A60-5FF6-4331-8DBD-4C7371783306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Mã NCC</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Tên NCC</t>
   </si>
@@ -47,19 +44,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -82,9 +73,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,17 +414,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,25 +436,20 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>